--- a/xuequ/fenxi/downloads/beijing-education-population-data.xlsx
+++ b/xuequ/fenxi/downloads/beijing-education-population-data.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="Ree74a157c6124068"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入学人口" sheetId="2" r:id="R987ad8c2d85f42f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高考人口" sheetId="3" r:id="Ra97d5a6747a54d50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本科实际录取" sheetId="4" r:id="Rbf378767e18343da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本科线上" sheetId="5" r:id="R96ae25b1dc8c4a07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内部核验" sheetId="6" r:id="Rbde2ec96acd14f83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公报交叉核验" sheetId="7" r:id="R06ee15552ec844de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="8" r:id="R40e4c16875e648b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R7b5db0b2e6a04f99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入学人口" sheetId="2" r:id="Rf3649b6671af4ff1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="高考人口" sheetId="3" r:id="Rff1b8b9294ef4618"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本科实际录取" sheetId="4" r:id="R8a46845bd1224743"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本科线上" sheetId="5" r:id="Rcfd141533ffe4a87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内部核验" sheetId="6" r:id="R9b9f5e5ff1854285"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公报交叉核验" sheetId="7" r:id="R453b495e941445fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="8" r:id="R3d087a29cc364114"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -93,7 +93,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -132,6 +132,13 @@
     </x:xf>
     <x:xf numFmtId="201" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -349,7 +356,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>版本：2026-07-20。网页主序列、原始来源与质量核验的可下载底表。</x:v>
+        <x:v>版本：2026-07-21。网页主序列、原始来源与质量核验的可下载底表。</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -403,7 +410,7 @@
         <x:v>本科线上</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>2020—2025年普通本科控制线及以上累计人数。</x:v>
+        <x:v>2020—2026年普通本科控制线及以上累计人数。</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
         <x:v>上线不等于最终录取。</x:v>
@@ -2263,19 +2270,19 @@
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
       <x:c r="A25" s="15" t="n">
-        <x:v>2018</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="B25" s="15" t="str">
-        <x:v>朝阳区</x:v>
+        <x:v>西城区</x:v>
       </x:c>
       <x:c r="C25" s="17" t="n">
-        <x:v>4000</x:v>
+        <x:v>9700</x:v>
       </x:c>
       <x:c r="D25" s="15" t="str">
-        <x:v>4,000余</x:v>
+        <x:v>9,700余</x:v>
       </x:c>
       <x:c r="E25" s="15" t="str">
-        <x:v>参加考试</x:v>
+        <x:v>报名考生</x:v>
       </x:c>
       <x:c r="F25" s="15" t="str">
         <x:v>lower_bound_rounded</x:v>
@@ -2284,21 +2291,21 @@
         <x:v>A</x:v>
       </x:c>
       <x:c r="H25" s="15" t="str">
-        <x:v>https://chyrd.bjchy.gov.cn/yfly/ff80808163d349de0163d7c6ad470001.html</x:v>
+        <x:v>https://www.bjxch.gov.cn/xcdt/xxxq/pnidpv999279.html</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
       <x:c r="A26" s="15" t="n">
-        <x:v>2022</x:v>
+        <x:v>2018</x:v>
       </x:c>
       <x:c r="B26" s="15" t="str">
         <x:v>朝阳区</x:v>
       </x:c>
       <x:c r="C26" s="17" t="n">
-        <x:v>4900</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D26" s="15" t="str">
-        <x:v>4,900余</x:v>
+        <x:v>4,000余</x:v>
       </x:c>
       <x:c r="E26" s="15" t="str">
         <x:v>参加考试</x:v>
@@ -2310,47 +2317,47 @@
         <x:v>A</x:v>
       </x:c>
       <x:c r="H26" s="15" t="str">
-        <x:v>https://chyrd.bjchy.gov.cn/yfly/8a24f0b481228d3c01816000ab0a00f0.html</x:v>
+        <x:v>https://chyrd.bjchy.gov.cn/yfly/ff80808163d349de0163d7c6ad470001.html</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
       <x:c r="A27" s="15" t="n">
-        <x:v>2024</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="B27" s="15" t="str">
         <x:v>朝阳区</x:v>
       </x:c>
       <x:c r="C27" s="17" t="n">
-        <x:v>6600</x:v>
+        <x:v>4900</x:v>
       </x:c>
       <x:c r="D27" s="15" t="str">
-        <x:v>6,600余</x:v>
+        <x:v>4,900余</x:v>
       </x:c>
       <x:c r="E27" s="15" t="str">
-        <x:v>参加高考（媒体参考）</x:v>
+        <x:v>参加考试</x:v>
       </x:c>
       <x:c r="F27" s="15" t="str">
         <x:v>lower_bound_rounded</x:v>
       </x:c>
       <x:c r="G27" s="15" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="H27" s="15" t="str">
-        <x:v>https://m.bjnews.com.cn/detail/1717715397129382.html</x:v>
+        <x:v>https://chyrd.bjchy.gov.cn/yfly/8a24f0b481228d3c01816000ab0a00f0.html</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
       <x:c r="A28" s="15" t="n">
-        <x:v>2025</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="B28" s="15" t="str">
         <x:v>朝阳区</x:v>
       </x:c>
       <x:c r="C28" s="17" t="n">
-        <x:v>8500</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="D28" s="15" t="str">
-        <x:v>8,500余</x:v>
+        <x:v>6,600余</x:v>
       </x:c>
       <x:c r="E28" s="15" t="str">
         <x:v>参加高考（媒体参考）</x:v>
@@ -2362,6 +2369,32 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="H28" s="15" t="str">
+        <x:v>https://m.bjnews.com.cn/detail/1717715397129382.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>朝阳区</x:v>
+      </x:c>
+      <x:c r="C29" s="19" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>8,500余</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>参加高考（媒体参考）</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>lower_bound_rounded</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
         <x:v>https://m.bjnews.com.cn/detail/1749261446168620.html</x:v>
       </x:c>
     </x:row>
@@ -2752,6 +2785,26 @@
       </x:c>
       <x:c r="F10" s="15" t="str">
         <x:v>https://www.bjeea.cn/uploads/soft/250625/172-2506250Q456.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="52" customHeight="1">
+      <x:c r="A11" s="20" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="B11" s="20" t="str">
+        <x:v>北京市</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="n">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="D11" s="21" t="n">
+        <x:v>59457</x:v>
+      </x:c>
+      <x:c r="E11" s="20" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="F11" s="20" t="str">
+        <x:v>https://www.bjeea.cn/uploads/soft/260625/2026%E5%B9%B4%E5%8C%97%E4%BA%AC%E5%B8%82%E9%AB%98%E8%80%83%E8%80%83%E7%94%9F%E5%88%86%E6%95%B0%E5%88%86%E5%B8%83.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
